--- a/Data/00C2_country_region.xlsx
+++ b/Data/00C2_country_region.xlsx
@@ -10,7 +10,7 @@
     <sheet sheetId="1" r:id="rId1" name="_00C2_country_region"/>
   </sheets>
   <definedNames>
-    <definedName name="_00C2_country_region">'_00C2_country_region'!$A$1:$G$229</definedName>
+    <definedName name="_00C2_country_region">'_00C2_country_region'!$A$1:$G$231</definedName>
   </definedNames>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
@@ -343,7 +343,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G233"/>
+  <dimension ref="A1:G231"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1068,16 +1068,16 @@
     <row outlineLevel="0" r="24">
       <c r="A24" s="0" t="inlineStr">
         <is>
-          <t>Equatorial Guinea</t>
+          <t>Congo_Brazzaville</t>
         </is>
       </c>
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="C24" s="0">
-        <v>226</v>
+        <v>178</v>
       </c>
       <c r="D24" s="0" t="inlineStr">
         <is>
@@ -1099,16 +1099,16 @@
     <row outlineLevel="0" r="25">
       <c r="A25" s="0" t="inlineStr">
         <is>
-          <t>Gabon</t>
+          <t>Congo_Kinshasa</t>
         </is>
       </c>
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="C25" s="0">
-        <v>266</v>
+        <v>180</v>
       </c>
       <c r="D25" s="0" t="inlineStr">
         <is>
@@ -1130,16 +1130,16 @@
     <row outlineLevel="0" r="26">
       <c r="A26" s="0" t="inlineStr">
         <is>
-          <t>Sao Tome and Principe</t>
+          <t>Equatorial Guinea</t>
         </is>
       </c>
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="C26" s="0">
-        <v>678</v>
+        <v>226</v>
       </c>
       <c r="D26" s="0" t="inlineStr">
         <is>
@@ -1161,16 +1161,16 @@
     <row outlineLevel="0" r="27">
       <c r="A27" s="0" t="inlineStr">
         <is>
-          <t>Algeria</t>
+          <t>Gabon</t>
         </is>
       </c>
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="C27" s="0">
-        <v>12</v>
+        <v>266</v>
       </c>
       <c r="D27" s="0" t="inlineStr">
         <is>
@@ -1182,26 +1182,26 @@
       </c>
       <c r="F27" s="0" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="G27" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="28">
       <c r="A28" s="0" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sao Tome and Principe</t>
         </is>
       </c>
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="C28" s="0">
-        <v>818</v>
+        <v>678</v>
       </c>
       <c r="D28" s="0" t="inlineStr">
         <is>
@@ -1213,26 +1213,26 @@
       </c>
       <c r="F28" s="0" t="inlineStr">
         <is>
-          <t>Northern Africa</t>
+          <t>Middle Africa</t>
         </is>
       </c>
       <c r="G28" s="0">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row outlineLevel="0" r="29">
       <c r="A29" s="0" t="inlineStr">
         <is>
-          <t>Libya</t>
+          <t>Algeria</t>
         </is>
       </c>
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="C29" s="0">
-        <v>434</v>
+        <v>12</v>
       </c>
       <c r="D29" s="0" t="inlineStr">
         <is>
@@ -1254,16 +1254,16 @@
     <row outlineLevel="0" r="30">
       <c r="A30" s="0" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="C30" s="0">
-        <v>504</v>
+        <v>818</v>
       </c>
       <c r="D30" s="0" t="inlineStr">
         <is>
@@ -1285,16 +1285,16 @@
     <row outlineLevel="0" r="31">
       <c r="A31" s="0" t="inlineStr">
         <is>
-          <t>Sudan</t>
+          <t>Libya</t>
         </is>
       </c>
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="C31" s="0">
-        <v>729</v>
+        <v>434</v>
       </c>
       <c r="D31" s="0" t="inlineStr">
         <is>
@@ -1316,16 +1316,16 @@
     <row outlineLevel="0" r="32">
       <c r="A32" s="0" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>Morocco</t>
         </is>
       </c>
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="C32" s="0">
-        <v>788</v>
+        <v>504</v>
       </c>
       <c r="D32" s="0" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
     <row outlineLevel="0" r="33">
       <c r="A33" s="0" t="inlineStr">
         <is>
-          <t>Botswana</t>
+          <t>Sudan</t>
         </is>
       </c>
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="C33" s="0">
-        <v>72</v>
+        <v>729</v>
       </c>
       <c r="D33" s="0" t="inlineStr">
         <is>
@@ -1368,26 +1368,26 @@
       </c>
       <c r="F33" s="0" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="G33" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="34">
       <c r="A34" s="0" t="inlineStr">
         <is>
-          <t>Eswatini</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="C34" s="0">
-        <v>748</v>
+        <v>788</v>
       </c>
       <c r="D34" s="0" t="inlineStr">
         <is>
@@ -1399,26 +1399,26 @@
       </c>
       <c r="F34" s="0" t="inlineStr">
         <is>
-          <t>Southern Africa</t>
+          <t>Northern Africa</t>
         </is>
       </c>
       <c r="G34" s="0">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row outlineLevel="0" r="35">
       <c r="A35" s="0" t="inlineStr">
         <is>
-          <t>Lesotho</t>
+          <t>Botswana</t>
         </is>
       </c>
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="C35" s="0">
-        <v>426</v>
+        <v>72</v>
       </c>
       <c r="D35" s="0" t="inlineStr">
         <is>
@@ -1440,16 +1440,16 @@
     <row outlineLevel="0" r="36">
       <c r="A36" s="0" t="inlineStr">
         <is>
-          <t>Namibia</t>
+          <t>Eswatini</t>
         </is>
       </c>
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="C36" s="0">
-        <v>516</v>
+        <v>748</v>
       </c>
       <c r="D36" s="0" t="inlineStr">
         <is>
@@ -1471,16 +1471,16 @@
     <row outlineLevel="0" r="37">
       <c r="A37" s="0" t="inlineStr">
         <is>
-          <t>South Africa</t>
+          <t>Lesotho</t>
         </is>
       </c>
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>ZAF</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="C37" s="0">
-        <v>710</v>
+        <v>426</v>
       </c>
       <c r="D37" s="0" t="inlineStr">
         <is>
@@ -1502,16 +1502,16 @@
     <row outlineLevel="0" r="38">
       <c r="A38" s="0" t="inlineStr">
         <is>
-          <t>Benin</t>
+          <t>Namibia</t>
         </is>
       </c>
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="C38" s="0">
-        <v>204</v>
+        <v>516</v>
       </c>
       <c r="D38" s="0" t="inlineStr">
         <is>
@@ -1523,26 +1523,26 @@
       </c>
       <c r="F38" s="0" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="G38" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="39">
       <c r="A39" s="0" t="inlineStr">
         <is>
-          <t>Burkina Faso</t>
+          <t>South Africa</t>
         </is>
       </c>
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="C39" s="0">
-        <v>854</v>
+        <v>710</v>
       </c>
       <c r="D39" s="0" t="inlineStr">
         <is>
@@ -1554,26 +1554,26 @@
       </c>
       <c r="F39" s="0" t="inlineStr">
         <is>
-          <t>Western Africa</t>
+          <t>Southern Africa</t>
         </is>
       </c>
       <c r="G39" s="0">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row outlineLevel="0" r="40">
       <c r="A40" s="0" t="inlineStr">
         <is>
-          <t>Cabo Verde</t>
+          <t>Benin</t>
         </is>
       </c>
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="C40" s="0">
-        <v>132</v>
+        <v>204</v>
       </c>
       <c r="D40" s="0" t="inlineStr">
         <is>
@@ -1595,16 +1595,16 @@
     <row outlineLevel="0" r="41">
       <c r="A41" s="0" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire</t>
+          <t>Burkina Faso</t>
         </is>
       </c>
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="C41" s="0">
-        <v>384</v>
+        <v>854</v>
       </c>
       <c r="D41" s="0" t="inlineStr">
         <is>
@@ -1626,16 +1626,16 @@
     <row outlineLevel="0" r="42">
       <c r="A42" s="0" t="inlineStr">
         <is>
-          <t>Gambia</t>
+          <t>Cabo Verde</t>
         </is>
       </c>
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="C42" s="0">
-        <v>270</v>
+        <v>132</v>
       </c>
       <c r="D42" s="0" t="inlineStr">
         <is>
@@ -1657,16 +1657,16 @@
     <row outlineLevel="0" r="43">
       <c r="A43" s="0" t="inlineStr">
         <is>
-          <t>Ghana</t>
+          <t>Cote d'Ivoire</t>
         </is>
       </c>
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="C43" s="0">
-        <v>288</v>
+        <v>384</v>
       </c>
       <c r="D43" s="0" t="inlineStr">
         <is>
@@ -1688,16 +1688,16 @@
     <row outlineLevel="0" r="44">
       <c r="A44" s="0" t="inlineStr">
         <is>
-          <t>Guinea</t>
+          <t>Gambia</t>
         </is>
       </c>
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="C44" s="0">
-        <v>324</v>
+        <v>270</v>
       </c>
       <c r="D44" s="0" t="inlineStr">
         <is>
@@ -1719,16 +1719,16 @@
     <row outlineLevel="0" r="45">
       <c r="A45" s="0" t="inlineStr">
         <is>
-          <t>Guinea-Bissau</t>
+          <t>Ghana</t>
         </is>
       </c>
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="C45" s="0">
-        <v>624</v>
+        <v>288</v>
       </c>
       <c r="D45" s="0" t="inlineStr">
         <is>
@@ -1750,16 +1750,16 @@
     <row outlineLevel="0" r="46">
       <c r="A46" s="0" t="inlineStr">
         <is>
-          <t>Liberia</t>
+          <t>Guinea</t>
         </is>
       </c>
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="C46" s="0">
-        <v>430</v>
+        <v>324</v>
       </c>
       <c r="D46" s="0" t="inlineStr">
         <is>
@@ -1781,16 +1781,16 @@
     <row outlineLevel="0" r="47">
       <c r="A47" s="0" t="inlineStr">
         <is>
-          <t>Mali</t>
+          <t>Guinea-Bissau</t>
         </is>
       </c>
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="C47" s="0">
-        <v>466</v>
+        <v>624</v>
       </c>
       <c r="D47" s="0" t="inlineStr">
         <is>
@@ -1812,16 +1812,16 @@
     <row outlineLevel="0" r="48">
       <c r="A48" s="0" t="inlineStr">
         <is>
-          <t>Mauritania</t>
+          <t>Liberia</t>
         </is>
       </c>
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="C48" s="0">
-        <v>478</v>
+        <v>430</v>
       </c>
       <c r="D48" s="0" t="inlineStr">
         <is>
@@ -1843,16 +1843,16 @@
     <row outlineLevel="0" r="49">
       <c r="A49" s="0" t="inlineStr">
         <is>
-          <t>Niger</t>
+          <t>Mali</t>
         </is>
       </c>
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="C49" s="0">
-        <v>562</v>
+        <v>466</v>
       </c>
       <c r="D49" s="0" t="inlineStr">
         <is>
@@ -1874,16 +1874,16 @@
     <row outlineLevel="0" r="50">
       <c r="A50" s="0" t="inlineStr">
         <is>
-          <t>Nigeria</t>
+          <t>Mauritania</t>
         </is>
       </c>
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="C50" s="0">
-        <v>566</v>
+        <v>478</v>
       </c>
       <c r="D50" s="0" t="inlineStr">
         <is>
@@ -1905,16 +1905,16 @@
     <row outlineLevel="0" r="51">
       <c r="A51" s="0" t="inlineStr">
         <is>
-          <t>Saint Helena</t>
+          <t>Niger</t>
         </is>
       </c>
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>SHN</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="C51" s="0">
-        <v>654</v>
+        <v>562</v>
       </c>
       <c r="D51" s="0" t="inlineStr">
         <is>
@@ -1936,16 +1936,16 @@
     <row outlineLevel="0" r="52">
       <c r="A52" s="0" t="inlineStr">
         <is>
-          <t>Senegal</t>
+          <t>Nigeria</t>
         </is>
       </c>
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="C52" s="0">
-        <v>686</v>
+        <v>566</v>
       </c>
       <c r="D52" s="0" t="inlineStr">
         <is>
@@ -1967,16 +1967,16 @@
     <row outlineLevel="0" r="53">
       <c r="A53" s="0" t="inlineStr">
         <is>
-          <t>Sierra Leone</t>
+          <t>Saint Helena</t>
         </is>
       </c>
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>SHN</t>
         </is>
       </c>
       <c r="C53" s="0">
-        <v>694</v>
+        <v>654</v>
       </c>
       <c r="D53" s="0" t="inlineStr">
         <is>
@@ -1998,16 +1998,16 @@
     <row outlineLevel="0" r="54">
       <c r="A54" s="0" t="inlineStr">
         <is>
-          <t>Togo</t>
+          <t>Senegal</t>
         </is>
       </c>
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="C54" s="0">
-        <v>768</v>
+        <v>686</v>
       </c>
       <c r="D54" s="0" t="inlineStr">
         <is>
@@ -2029,78 +2029,78 @@
     <row outlineLevel="0" r="55">
       <c r="A55" s="0" t="inlineStr">
         <is>
-          <t>Anguilla</t>
+          <t>Sierra Leone</t>
         </is>
       </c>
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>AIA</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="C55" s="0">
-        <v>660</v>
+        <v>694</v>
       </c>
       <c r="D55" s="0" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E55" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F55" s="0" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="G55" s="0">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="56">
       <c r="A56" s="0" t="inlineStr">
         <is>
-          <t>Antigua and Barbuda</t>
+          <t>Togo</t>
         </is>
       </c>
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="C56" s="0">
-        <v>28</v>
+        <v>768</v>
       </c>
       <c r="D56" s="0" t="inlineStr">
         <is>
-          <t>Americas</t>
+          <t>Africa</t>
         </is>
       </c>
       <c r="E56" s="0">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F56" s="0" t="inlineStr">
         <is>
-          <t>Caribbean</t>
+          <t>Western Africa</t>
         </is>
       </c>
       <c r="G56" s="0">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row outlineLevel="0" r="57">
       <c r="A57" s="0" t="inlineStr">
         <is>
-          <t>Aruba</t>
+          <t>Anguilla</t>
         </is>
       </c>
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>ABW</t>
+          <t>AIA</t>
         </is>
       </c>
       <c r="C57" s="0">
-        <v>533</v>
+        <v>660</v>
       </c>
       <c r="D57" s="0" t="inlineStr">
         <is>
@@ -2122,16 +2122,16 @@
     <row outlineLevel="0" r="58">
       <c r="A58" s="0" t="inlineStr">
         <is>
-          <t>Bahamas</t>
+          <t>Antigua and Barbuda</t>
         </is>
       </c>
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="C58" s="0">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D58" s="0" t="inlineStr">
         <is>
@@ -2153,16 +2153,16 @@
     <row outlineLevel="0" r="59">
       <c r="A59" s="0" t="inlineStr">
         <is>
-          <t>Barbados</t>
+          <t>Aruba</t>
         </is>
       </c>
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>ABW</t>
         </is>
       </c>
       <c r="C59" s="0">
-        <v>52</v>
+        <v>533</v>
       </c>
       <c r="D59" s="0" t="inlineStr">
         <is>
@@ -2184,16 +2184,16 @@
     <row outlineLevel="0" r="60">
       <c r="A60" s="0" t="inlineStr">
         <is>
-          <t>Cayman Islands</t>
+          <t>Bahamas</t>
         </is>
       </c>
       <c r="B60" s="0" t="inlineStr">
         <is>
-          <t>CYM</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="C60" s="0">
-        <v>136</v>
+        <v>44</v>
       </c>
       <c r="D60" s="0" t="inlineStr">
         <is>
@@ -2215,16 +2215,16 @@
     <row outlineLevel="0" r="61">
       <c r="A61" s="0" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Barbados</t>
         </is>
       </c>
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="C61" s="0">
-        <v>192</v>
+        <v>52</v>
       </c>
       <c r="D61" s="0" t="inlineStr">
         <is>
@@ -2246,16 +2246,16 @@
     <row outlineLevel="0" r="62">
       <c r="A62" s="0" t="inlineStr">
         <is>
-          <t>Curacao</t>
+          <t>Cayman Islands</t>
         </is>
       </c>
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>CUW</t>
+          <t>CYM</t>
         </is>
       </c>
       <c r="C62" s="0">
-        <v>531</v>
+        <v>136</v>
       </c>
       <c r="D62" s="0" t="inlineStr">
         <is>
@@ -2277,16 +2277,16 @@
     <row outlineLevel="0" r="63">
       <c r="A63" s="0" t="inlineStr">
         <is>
-          <t>Dominica</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>DMA</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="C63" s="0">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="D63" s="0" t="inlineStr">
         <is>
@@ -2308,16 +2308,16 @@
     <row outlineLevel="0" r="64">
       <c r="A64" s="0" t="inlineStr">
         <is>
-          <t>Dominican Republic</t>
+          <t>Curacao</t>
         </is>
       </c>
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>CUW</t>
         </is>
       </c>
       <c r="C64" s="0">
-        <v>214</v>
+        <v>531</v>
       </c>
       <c r="D64" s="0" t="inlineStr">
         <is>
@@ -2339,16 +2339,16 @@
     <row outlineLevel="0" r="65">
       <c r="A65" s="0" t="inlineStr">
         <is>
-          <t>Grenada</t>
+          <t>Dominica</t>
         </is>
       </c>
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>DMA</t>
         </is>
       </c>
       <c r="C65" s="0">
-        <v>308</v>
+        <v>212</v>
       </c>
       <c r="D65" s="0" t="inlineStr">
         <is>
@@ -2370,16 +2370,16 @@
     <row outlineLevel="0" r="66">
       <c r="A66" s="0" t="inlineStr">
         <is>
-          <t>Haiti</t>
+          <t>Dominican Republic</t>
         </is>
       </c>
       <c r="B66" s="0" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="C66" s="0">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="D66" s="0" t="inlineStr">
         <is>
@@ -2401,16 +2401,16 @@
     <row outlineLevel="0" r="67">
       <c r="A67" s="0" t="inlineStr">
         <is>
-          <t>Jamaica</t>
+          <t>Grenada</t>
         </is>
       </c>
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="C67" s="0">
-        <v>388</v>
+        <v>308</v>
       </c>
       <c r="D67" s="0" t="inlineStr">
         <is>
@@ -2432,16 +2432,16 @@
     <row outlineLevel="0" r="68">
       <c r="A68" s="0" t="inlineStr">
         <is>
-          <t>Montserrat</t>
+          <t>Haiti</t>
         </is>
       </c>
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>MSR</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="C68" s="0">
-        <v>500</v>
+        <v>332</v>
       </c>
       <c r="D68" s="0" t="inlineStr">
         <is>
@@ -2463,16 +2463,16 @@
     <row outlineLevel="0" r="69">
       <c r="A69" s="0" t="inlineStr">
         <is>
-          <t>Puerto Rico</t>
+          <t>Jamaica</t>
         </is>
       </c>
       <c r="B69" s="0" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="C69" s="0">
-        <v>630</v>
+        <v>388</v>
       </c>
       <c r="D69" s="0" t="inlineStr">
         <is>
@@ -2494,16 +2494,16 @@
     <row outlineLevel="0" r="70">
       <c r="A70" s="0" t="inlineStr">
         <is>
-          <t>Saint Barthelemy</t>
+          <t>Montserrat</t>
         </is>
       </c>
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>BLM</t>
+          <t>MSR</t>
         </is>
       </c>
       <c r="C70" s="0">
-        <v>652</v>
+        <v>500</v>
       </c>
       <c r="D70" s="0" t="inlineStr">
         <is>
@@ -2525,16 +2525,16 @@
     <row outlineLevel="0" r="71">
       <c r="A71" s="0" t="inlineStr">
         <is>
-          <t>Saint Kitts and Nevis</t>
+          <t>Puerto Rico</t>
         </is>
       </c>
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>KNA</t>
+          <t>PRI</t>
         </is>
       </c>
       <c r="C71" s="0">
-        <v>659</v>
+        <v>630</v>
       </c>
       <c r="D71" s="0" t="inlineStr">
         <is>
@@ -2556,16 +2556,16 @@
     <row outlineLevel="0" r="72">
       <c r="A72" s="0" t="inlineStr">
         <is>
-          <t>Saint Lucia</t>
+          <t>Saint Barthelemy</t>
         </is>
       </c>
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>BLM</t>
         </is>
       </c>
       <c r="C72" s="0">
-        <v>662</v>
+        <v>652</v>
       </c>
       <c r="D72" s="0" t="inlineStr">
         <is>
@@ -2587,16 +2587,16 @@
     <row outlineLevel="0" r="73">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>Saint Martin</t>
+          <t>Saint Kitts and Nevis</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>MAF</t>
+          <t>KNA</t>
         </is>
       </c>
       <c r="C73" s="0">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
@@ -2618,16 +2618,16 @@
     <row outlineLevel="0" r="74">
       <c r="A74" s="0" t="inlineStr">
         <is>
-          <t>Saint Vincent and the Grenadines</t>
+          <t>Saint Lucia</t>
         </is>
       </c>
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>VCT</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="C74" s="0">
-        <v>670</v>
+        <v>662</v>
       </c>
       <c r="D74" s="0" t="inlineStr">
         <is>
@@ -2649,16 +2649,16 @@
     <row outlineLevel="0" r="75">
       <c r="A75" s="0" t="inlineStr">
         <is>
-          <t>Sint Maarten</t>
+          <t>Saint Martin</t>
         </is>
       </c>
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>SXM</t>
+          <t>MAF</t>
         </is>
       </c>
       <c r="C75" s="0">
-        <v>534</v>
+        <v>663</v>
       </c>
       <c r="D75" s="0" t="inlineStr">
         <is>
@@ -2680,16 +2680,16 @@
     <row outlineLevel="0" r="76">
       <c r="A76" s="0" t="inlineStr">
         <is>
-          <t>Trinidad and Tobago</t>
+          <t>Saint Vincent and the Grenadines</t>
         </is>
       </c>
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="C76" s="0">
-        <v>780</v>
+        <v>670</v>
       </c>
       <c r="D76" s="0" t="inlineStr">
         <is>
@@ -2711,16 +2711,16 @@
     <row outlineLevel="0" r="77">
       <c r="A77" s="0" t="inlineStr">
         <is>
-          <t>Turks and Caicos Islands</t>
+          <t>Sint Maarten</t>
         </is>
       </c>
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>TCA</t>
+          <t>SXM</t>
         </is>
       </c>
       <c r="C77" s="0">
-        <v>796</v>
+        <v>534</v>
       </c>
       <c r="D77" s="0" t="inlineStr">
         <is>
@@ -2742,16 +2742,16 @@
     <row outlineLevel="0" r="78">
       <c r="A78" s="0" t="inlineStr">
         <is>
-          <t>Virgin Islands, British</t>
+          <t>Trinidad and Tobago</t>
         </is>
       </c>
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>VGB</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="C78" s="0">
-        <v>92</v>
+        <v>780</v>
       </c>
       <c r="D78" s="0" t="inlineStr">
         <is>
@@ -2773,16 +2773,16 @@
     <row outlineLevel="0" r="79">
       <c r="A79" s="0" t="inlineStr">
         <is>
-          <t>Virgin Islands, U.S.</t>
+          <t>Turks and Caicos Islands</t>
         </is>
       </c>
       <c r="B79" s="0" t="inlineStr">
         <is>
-          <t>VIR</t>
+          <t>TCA</t>
         </is>
       </c>
       <c r="C79" s="0">
-        <v>850</v>
+        <v>796</v>
       </c>
       <c r="D79" s="0" t="inlineStr">
         <is>
@@ -2804,16 +2804,16 @@
     <row outlineLevel="0" r="80">
       <c r="A80" s="0" t="inlineStr">
         <is>
-          <t>Belize</t>
+          <t>Virgin Islands, British</t>
         </is>
       </c>
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>VGB</t>
         </is>
       </c>
       <c r="C80" s="0">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="D80" s="0" t="inlineStr">
         <is>
@@ -2825,26 +2825,26 @@
       </c>
       <c r="F80" s="0" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="G80" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="81">
       <c r="A81" s="0" t="inlineStr">
         <is>
-          <t>Costa Rica</t>
+          <t>Virgin Islands, U.S.</t>
         </is>
       </c>
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="C81" s="0">
-        <v>188</v>
+        <v>850</v>
       </c>
       <c r="D81" s="0" t="inlineStr">
         <is>
@@ -2856,26 +2856,26 @@
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>Central America</t>
+          <t>Caribbean</t>
         </is>
       </c>
       <c r="G81" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row outlineLevel="0" r="82">
       <c r="A82" s="0" t="inlineStr">
         <is>
-          <t>El Salvador</t>
+          <t>Belize</t>
         </is>
       </c>
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="C82" s="0">
-        <v>222</v>
+        <v>84</v>
       </c>
       <c r="D82" s="0" t="inlineStr">
         <is>
@@ -2897,16 +2897,16 @@
     <row outlineLevel="0" r="83">
       <c r="A83" s="0" t="inlineStr">
         <is>
-          <t>Guatemala</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="C83" s="0">
-        <v>320</v>
+        <v>188</v>
       </c>
       <c r="D83" s="0" t="inlineStr">
         <is>
@@ -2928,16 +2928,16 @@
     <row outlineLevel="0" r="84">
       <c r="A84" s="0" t="inlineStr">
         <is>
-          <t>Honduras</t>
+          <t>El Salvador</t>
         </is>
       </c>
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="C84" s="0">
-        <v>340</v>
+        <v>222</v>
       </c>
       <c r="D84" s="0" t="inlineStr">
         <is>
@@ -2959,16 +2959,16 @@
     <row outlineLevel="0" r="85">
       <c r="A85" s="0" t="inlineStr">
         <is>
-          <t>Mexico</t>
+          <t>Guatemala</t>
         </is>
       </c>
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="C85" s="0">
-        <v>484</v>
+        <v>320</v>
       </c>
       <c r="D85" s="0" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
     <row outlineLevel="0" r="86">
       <c r="A86" s="0" t="inlineStr">
         <is>
-          <t>Nicaragua</t>
+          <t>Honduras</t>
         </is>
       </c>
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="C86" s="0">
-        <v>558</v>
+        <v>340</v>
       </c>
       <c r="D86" s="0" t="inlineStr">
         <is>
@@ -3021,16 +3021,16 @@
     <row outlineLevel="0" r="87">
       <c r="A87" s="0" t="inlineStr">
         <is>
-          <t>Panama</t>
+          <t>Mexico</t>
         </is>
       </c>
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="C87" s="0">
-        <v>591</v>
+        <v>484</v>
       </c>
       <c r="D87" s="0" t="inlineStr">
         <is>
@@ -3052,78 +3052,78 @@
     <row outlineLevel="0" r="88">
       <c r="A88" s="0" t="inlineStr">
         <is>
-          <t>Kazakhstan</t>
+          <t>Nicaragua</t>
         </is>
       </c>
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="C88" s="0">
-        <v>398</v>
+        <v>558</v>
       </c>
       <c r="D88" s="0" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="E88" s="0">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="G88" s="0">
-        <v>143</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="89">
       <c r="A89" s="0" t="inlineStr">
         <is>
-          <t>Kyrgyzstan</t>
+          <t>Panama</t>
         </is>
       </c>
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="C89" s="0">
-        <v>417</v>
+        <v>591</v>
       </c>
       <c r="D89" s="0" t="inlineStr">
         <is>
-          <t>Asia</t>
+          <t>Americas</t>
         </is>
       </c>
       <c r="E89" s="0">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t>Central Asia</t>
+          <t>Central America</t>
         </is>
       </c>
       <c r="G89" s="0">
-        <v>143</v>
+        <v>13</v>
       </c>
     </row>
     <row outlineLevel="0" r="90">
       <c r="A90" s="0" t="inlineStr">
         <is>
-          <t>Tajikistan</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="C90" s="0">
-        <v>762</v>
+        <v>398</v>
       </c>
       <c r="D90" s="0" t="inlineStr">
         <is>
@@ -3145,16 +3145,16 @@
     <row outlineLevel="0" r="91">
       <c r="A91" s="0" t="inlineStr">
         <is>
-          <t>Turkmenistan</t>
+          <t>Kyrgyzstan</t>
         </is>
       </c>
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="C91" s="0">
-        <v>795</v>
+        <v>417</v>
       </c>
       <c r="D91" s="0" t="inlineStr">
         <is>
@@ -3176,16 +3176,16 @@
     <row outlineLevel="0" r="92">
       <c r="A92" s="0" t="inlineStr">
         <is>
-          <t>Uzbekistan</t>
+          <t>Tajikistan</t>
         </is>
       </c>
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="C92" s="0">
-        <v>860</v>
+        <v>762</v>
       </c>
       <c r="D92" s="0" t="inlineStr">
         <is>
@@ -3207,16 +3207,16 @@
     <row outlineLevel="0" r="93">
       <c r="A93" s="0" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Turkmenistan</t>
         </is>
       </c>
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="C93" s="0">
-        <v>156</v>
+        <v>795</v>
       </c>
       <c r="D93" s="0" t="inlineStr">
         <is>
@@ -3228,26 +3228,26 @@
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="G93" s="0">
-        <v>30</v>
+        <v>143</v>
       </c>
     </row>
     <row outlineLevel="0" r="94">
       <c r="A94" s="0" t="inlineStr">
         <is>
-          <t>Hong Kong</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="C94" s="0">
-        <v>344</v>
+        <v>860</v>
       </c>
       <c r="D94" s="0" t="inlineStr">
         <is>
@@ -3259,26 +3259,26 @@
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t>Eastern Asia</t>
+          <t>Central Asia</t>
         </is>
       </c>
       <c r="G94" s="0">
-        <v>30</v>
+        <v>143</v>
       </c>
     </row>
     <row outlineLevel="0" r="95">
       <c r="A95" s="0" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>China</t>
         </is>
       </c>
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="C95" s="0">
-        <v>392</v>
+        <v>156</v>
       </c>
       <c r="D95" s="0" t="inlineStr">
         <is>
@@ -3300,16 +3300,16 @@
     <row outlineLevel="0" r="96">
       <c r="A96" s="0" t="inlineStr">
         <is>
-          <t>Korea, North</t>
+          <t>Hong Kong</t>
         </is>
       </c>
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>PRK</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="C96" s="0">
-        <v>408</v>
+        <v>344</v>
       </c>
       <c r="D96" s="0" t="inlineStr">
         <is>
@@ -3331,16 +3331,16 @@
     <row outlineLevel="0" r="97">
       <c r="A97" s="0" t="inlineStr">
         <is>
-          <t>Korea, South</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="C97" s="0">
-        <v>410</v>
+        <v>392</v>
       </c>
       <c r="D97" s="0" t="inlineStr">
         <is>
@@ -3362,16 +3362,16 @@
     <row outlineLevel="0" r="98">
       <c r="A98" s="0" t="inlineStr">
         <is>
-          <t>Macau</t>
+          <t>Korea, North</t>
         </is>
       </c>
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>MAC</t>
+          <t>PRK</t>
         </is>
       </c>
       <c r="C98" s="0">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="D98" s="0" t="inlineStr">
         <is>
@@ -3393,16 +3393,16 @@
     <row outlineLevel="0" r="99">
       <c r="A99" s="0" t="inlineStr">
         <is>
-          <t>Mongolia</t>
+          <t>Korea, South</t>
         </is>
       </c>
       <c r="B99" s="0" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="C99" s="0">
-        <v>496</v>
+        <v>410</v>
       </c>
       <c r="D99" s="0" t="inlineStr">
         <is>
@@ -3424,16 +3424,16 @@
     <row outlineLevel="0" r="100">
       <c r="A100" s="0" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Macau</t>
         </is>
       </c>
       <c r="B100" s="0" t="inlineStr">
         <is>
-          <t>TAIW</t>
+          <t>MAC</t>
         </is>
       </c>
       <c r="C100" s="0">
-        <v>156</v>
+        <v>446</v>
       </c>
       <c r="D100" s="0" t="inlineStr">
         <is>
@@ -3455,16 +3455,16 @@
     <row outlineLevel="0" r="101">
       <c r="A101" s="0" t="inlineStr">
         <is>
-          <t>Brunei</t>
+          <t>Mongolia</t>
         </is>
       </c>
       <c r="B101" s="0" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="C101" s="0">
-        <v>96</v>
+        <v>496</v>
       </c>
       <c r="D101" s="0" t="inlineStr">
         <is>
@@ -3476,26 +3476,26 @@
       </c>
       <c r="F101" s="0" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="G101" s="0">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="102">
       <c r="A102" s="0" t="inlineStr">
         <is>
-          <t>Cambodia</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="B102" s="0" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>TAIW</t>
         </is>
       </c>
       <c r="C102" s="0">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="D102" s="0" t="inlineStr">
         <is>
@@ -3507,26 +3507,26 @@
       </c>
       <c r="F102" s="0" t="inlineStr">
         <is>
-          <t>South-eastern Asia</t>
+          <t>Eastern Asia</t>
         </is>
       </c>
       <c r="G102" s="0">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row outlineLevel="0" r="103">
       <c r="A103" s="0" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Brunei</t>
         </is>
       </c>
       <c r="B103" s="0" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="C103" s="0">
-        <v>360</v>
+        <v>96</v>
       </c>
       <c r="D103" s="0" t="inlineStr">
         <is>
@@ -3548,16 +3548,16 @@
     <row outlineLevel="0" r="104">
       <c r="A104" s="0" t="inlineStr">
         <is>
-          <t>Laos</t>
+          <t>Cambodia</t>
         </is>
       </c>
       <c r="B104" s="0" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="C104" s="0">
-        <v>418</v>
+        <v>116</v>
       </c>
       <c r="D104" s="0" t="inlineStr">
         <is>
@@ -3579,16 +3579,16 @@
     <row outlineLevel="0" r="105">
       <c r="A105" s="0" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="B105" s="0" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="C105" s="0">
-        <v>458</v>
+        <v>360</v>
       </c>
       <c r="D105" s="0" t="inlineStr">
         <is>
@@ -3610,16 +3610,16 @@
     <row outlineLevel="0" r="106">
       <c r="A106" s="0" t="inlineStr">
         <is>
-          <t>Myanmar</t>
+          <t>Laos</t>
         </is>
       </c>
       <c r="B106" s="0" t="inlineStr">
         <is>
-          <t>MMR</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="C106" s="0">
-        <v>104</v>
+        <v>418</v>
       </c>
       <c r="D106" s="0" t="inlineStr">
         <is>
@@ -3641,16 +3641,16 @@
     <row outlineLevel="0" r="107">
       <c r="A107" s="0" t="inlineStr">
         <is>
-          <t>Philippines</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="B107" s="0" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="C107" s="0">
-        <v>608</v>
+        <v>458</v>
       </c>
       <c r="D107" s="0" t="inlineStr">
         <is>
@@ -3672,16 +3672,16 @@
     <row outlineLevel="0" r="108">
       <c r="A108" s="0" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Myanmar</t>
         </is>
       </c>
       <c r="B108" s="0" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>MMR</t>
         </is>
       </c>
       <c r="C108" s="0">
-        <v>702</v>
+        <v>104</v>
       </c>
       <c r="D108" s="0" t="inlineStr">
         <is>
@@ -3703,16 +3703,16 @@
     <row outlineLevel="0" r="109">
       <c r="A109" s="0" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Philippines</t>
         </is>
       </c>
       <c r="B109" s="0" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="C109" s="0">
-        <v>764</v>
+        <v>608</v>
       </c>
       <c r="D109" s="0" t="inlineStr">
         <is>
@@ -3734,16 +3734,16 @@
     <row outlineLevel="0" r="110">
       <c r="A110" s="0" t="inlineStr">
         <is>
-          <t>Timor-Leste</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="B110" s="0" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="C110" s="0">
-        <v>626</v>
+        <v>702</v>
       </c>
       <c r="D110" s="0" t="inlineStr">
         <is>
@@ -3765,16 +3765,16 @@
     <row outlineLevel="0" r="111">
       <c r="A111" s="0" t="inlineStr">
         <is>
-          <t>Vietnam</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="B111" s="0" t="inlineStr">
         <is>
-          <t>VNM</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="C111" s="0">
-        <v>704</v>
+        <v>764</v>
       </c>
       <c r="D111" s="0" t="inlineStr">
         <is>
@@ -3796,16 +3796,16 @@
     <row outlineLevel="0" r="112">
       <c r="A112" s="0" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Timor-Leste</t>
         </is>
       </c>
       <c r="B112" s="0" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="C112" s="0">
-        <v>4</v>
+        <v>626</v>
       </c>
       <c r="D112" s="0" t="inlineStr">
         <is>
@@ -3817,26 +3817,26 @@
       </c>
       <c r="F112" s="0" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="G112" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="113">
       <c r="A113" s="0" t="inlineStr">
         <is>
-          <t>Bangladesh</t>
+          <t>Vietnam</t>
         </is>
       </c>
       <c r="B113" s="0" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="C113" s="0">
-        <v>50</v>
+        <v>704</v>
       </c>
       <c r="D113" s="0" t="inlineStr">
         <is>
@@ -3848,26 +3848,26 @@
       </c>
       <c r="F113" s="0" t="inlineStr">
         <is>
-          <t>Southern Asia</t>
+          <t>South-eastern Asia</t>
         </is>
       </c>
       <c r="G113" s="0">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row outlineLevel="0" r="114">
       <c r="A114" s="0" t="inlineStr">
         <is>
-          <t>Bhutan</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="B114" s="0" t="inlineStr">
         <is>
-          <t>BTN</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="C114" s="0">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="D114" s="0" t="inlineStr">
         <is>
@@ -3889,16 +3889,16 @@
     <row outlineLevel="0" r="115">
       <c r="A115" s="0" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Bangladesh</t>
         </is>
       </c>
       <c r="B115" s="0" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="C115" s="0">
-        <v>356</v>
+        <v>50</v>
       </c>
       <c r="D115" s="0" t="inlineStr">
         <is>
@@ -3920,16 +3920,16 @@
     <row outlineLevel="0" r="116">
       <c r="A116" s="0" t="inlineStr">
         <is>
-          <t>Iran</t>
+          <t>Bhutan</t>
         </is>
       </c>
       <c r="B116" s="0" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>BTN</t>
         </is>
       </c>
       <c r="C116" s="0">
-        <v>364</v>
+        <v>64</v>
       </c>
       <c r="D116" s="0" t="inlineStr">
         <is>
@@ -3951,16 +3951,16 @@
     <row outlineLevel="0" r="117">
       <c r="A117" s="0" t="inlineStr">
         <is>
-          <t>Maldives</t>
+          <t>India</t>
         </is>
       </c>
       <c r="B117" s="0" t="inlineStr">
         <is>
-          <t>MDV</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="C117" s="0">
-        <v>462</v>
+        <v>356</v>
       </c>
       <c r="D117" s="0" t="inlineStr">
         <is>
@@ -3982,16 +3982,16 @@
     <row outlineLevel="0" r="118">
       <c r="A118" s="0" t="inlineStr">
         <is>
-          <t>Nepal</t>
+          <t>Iran</t>
         </is>
       </c>
       <c r="B118" s="0" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="C118" s="0">
-        <v>524</v>
+        <v>364</v>
       </c>
       <c r="D118" s="0" t="inlineStr">
         <is>
@@ -4013,16 +4013,16 @@
     <row outlineLevel="0" r="119">
       <c r="A119" s="0" t="inlineStr">
         <is>
-          <t>Pakistan</t>
+          <t>Maldives</t>
         </is>
       </c>
       <c r="B119" s="0" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>MDV</t>
         </is>
       </c>
       <c r="C119" s="0">
-        <v>586</v>
+        <v>462</v>
       </c>
       <c r="D119" s="0" t="inlineStr">
         <is>
@@ -4044,16 +4044,16 @@
     <row outlineLevel="0" r="120">
       <c r="A120" s="0" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Nepal</t>
         </is>
       </c>
       <c r="B120" s="0" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="C120" s="0">
-        <v>144</v>
+        <v>524</v>
       </c>
       <c r="D120" s="0" t="inlineStr">
         <is>
@@ -4075,16 +4075,16 @@
     <row outlineLevel="0" r="121">
       <c r="A121" s="0" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Pakistan</t>
         </is>
       </c>
       <c r="B121" s="0" t="inlineStr">
         <is>
-          <t>ARM</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="C121" s="0">
-        <v>51</v>
+        <v>586</v>
       </c>
       <c r="D121" s="0" t="inlineStr">
         <is>
@@ -4096,26 +4096,26 @@
       </c>
       <c r="F121" s="0" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="G121" s="0">
-        <v>145</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="122">
       <c r="A122" s="0" t="inlineStr">
         <is>
-          <t>Azerbaijan</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="B122" s="0" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="C122" s="0">
-        <v>31</v>
+        <v>144</v>
       </c>
       <c r="D122" s="0" t="inlineStr">
         <is>
@@ -4127,26 +4127,26 @@
       </c>
       <c r="F122" s="0" t="inlineStr">
         <is>
-          <t>Western Asia</t>
+          <t>Southern Asia</t>
         </is>
       </c>
       <c r="G122" s="0">
-        <v>145</v>
+        <v>34</v>
       </c>
     </row>
     <row outlineLevel="0" r="123">
       <c r="A123" s="0" t="inlineStr">
         <is>
-          <t>Bahrain</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="B123" s="0" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>ARM</t>
         </is>
       </c>
       <c r="C123" s="0">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D123" s="0" t="inlineStr">
         <is>
@@ -4168,16 +4168,16 @@
     <row outlineLevel="0" r="124">
       <c r="A124" s="0" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Azerbaijan</t>
         </is>
       </c>
       <c r="B124" s="0" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="C124" s="0">
-        <v>196</v>
+        <v>31</v>
       </c>
       <c r="D124" s="0" t="inlineStr">
         <is>
@@ -4199,16 +4199,16 @@
     <row outlineLevel="0" r="125">
       <c r="A125" s="0" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Bahrain</t>
         </is>
       </c>
       <c r="B125" s="0" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="C125" s="0">
-        <v>268</v>
+        <v>48</v>
       </c>
       <c r="D125" s="0" t="inlineStr">
         <is>
@@ -4230,16 +4230,16 @@
     <row outlineLevel="0" r="126">
       <c r="A126" s="0" t="inlineStr">
         <is>
-          <t>Iraq</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="B126" s="0" t="inlineStr">
         <is>
-          <t>IRQ</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="C126" s="0">
-        <v>368</v>
+        <v>196</v>
       </c>
       <c r="D126" s="0" t="inlineStr">
         <is>
@@ -4261,16 +4261,16 @@
     <row outlineLevel="0" r="127">
       <c r="A127" s="0" t="inlineStr">
         <is>
-          <t>Israel</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="B127" s="0" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="C127" s="0">
-        <v>376</v>
+        <v>268</v>
       </c>
       <c r="D127" s="0" t="inlineStr">
         <is>
@@ -4292,16 +4292,16 @@
     <row outlineLevel="0" r="128">
       <c r="A128" s="0" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>Iraq</t>
         </is>
       </c>
       <c r="B128" s="0" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>IRQ</t>
         </is>
       </c>
       <c r="C128" s="0">
-        <v>400</v>
+        <v>368</v>
       </c>
       <c r="D128" s="0" t="inlineStr">
         <is>
@@ -4323,16 +4323,16 @@
     <row outlineLevel="0" r="129">
       <c r="A129" s="0" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>Israel</t>
         </is>
       </c>
       <c r="B129" s="0" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="C129" s="0">
-        <v>414</v>
+        <v>376</v>
       </c>
       <c r="D129" s="0" t="inlineStr">
         <is>
@@ -4354,16 +4354,16 @@
     <row outlineLevel="0" r="130">
       <c r="A130" s="0" t="inlineStr">
         <is>
-          <t>Lebanon</t>
+          <t>Jordan</t>
         </is>
       </c>
       <c r="B130" s="0" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="C130" s="0">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="D130" s="0" t="inlineStr">
         <is>
@@ -4385,16 +4385,16 @@
     <row outlineLevel="0" r="131">
       <c r="A131" s="0" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>Kuwait</t>
         </is>
       </c>
       <c r="B131" s="0" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="C131" s="0">
-        <v>512</v>
+        <v>414</v>
       </c>
       <c r="D131" s="0" t="inlineStr">
         <is>
@@ -4416,16 +4416,16 @@
     <row outlineLevel="0" r="132">
       <c r="A132" s="0" t="inlineStr">
         <is>
-          <t>Qatar</t>
+          <t>Lebanon</t>
         </is>
       </c>
       <c r="B132" s="0" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="C132" s="0">
-        <v>634</v>
+        <v>422</v>
       </c>
       <c r="D132" s="0" t="inlineStr">
         <is>
@@ -4447,16 +4447,16 @@
     <row outlineLevel="0" r="133">
       <c r="A133" s="0" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>Oman</t>
         </is>
       </c>
       <c r="B133" s="0" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="C133" s="0">
-        <v>682</v>
+        <v>512</v>
       </c>
       <c r="D133" s="0" t="inlineStr">
         <is>
@@ -4478,16 +4478,16 @@
     <row outlineLevel="0" r="134">
       <c r="A134" s="0" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Qatar</t>
         </is>
       </c>
       <c r="B134" s="0" t="inlineStr">
         <is>
-          <t>SYR</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="C134" s="0">
-        <v>760</v>
+        <v>634</v>
       </c>
       <c r="D134" s="0" t="inlineStr">
         <is>
@@ -4509,16 +4509,16 @@
     <row outlineLevel="0" r="135">
       <c r="A135" s="0" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>Saudi Arabia</t>
         </is>
       </c>
       <c r="B135" s="0" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="C135" s="0">
-        <v>792</v>
+        <v>682</v>
       </c>
       <c r="D135" s="0" t="inlineStr">
         <is>
@@ -4540,16 +4540,16 @@
     <row outlineLevel="0" r="136">
       <c r="A136" s="0" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="B136" s="0" t="inlineStr">
         <is>
-          <t>ARE</t>
+          <t>SYR</t>
         </is>
       </c>
       <c r="C136" s="0">
-        <v>784</v>
+        <v>760</v>
       </c>
       <c r="D136" s="0" t="inlineStr">
         <is>
@@ -4571,16 +4571,16 @@
     <row outlineLevel="0" r="137">
       <c r="A137" s="0" t="inlineStr">
         <is>
-          <t>Yemen</t>
+          <t>Turkey</t>
         </is>
       </c>
       <c r="B137" s="0" t="inlineStr">
         <is>
-          <t>YEM</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="C137" s="0">
-        <v>887</v>
+        <v>792</v>
       </c>
       <c r="D137" s="0" t="inlineStr">
         <is>
@@ -4602,78 +4602,78 @@
     <row outlineLevel="0" r="138">
       <c r="A138" s="0" t="inlineStr">
         <is>
-          <t>Belarus</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="B138" s="0" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>ARE</t>
         </is>
       </c>
       <c r="C138" s="0">
-        <v>112</v>
+        <v>784</v>
       </c>
       <c r="D138" s="0" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="E138" s="0">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F138" s="0" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="G138" s="0">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row outlineLevel="0" r="139">
       <c r="A139" s="0" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Yemen</t>
         </is>
       </c>
       <c r="B139" s="0" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>YEM</t>
         </is>
       </c>
       <c r="C139" s="0">
-        <v>100</v>
+        <v>887</v>
       </c>
       <c r="D139" s="0" t="inlineStr">
         <is>
-          <t>Europe</t>
+          <t>Asia</t>
         </is>
       </c>
       <c r="E139" s="0">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F139" s="0" t="inlineStr">
         <is>
-          <t>Eastern Europe</t>
+          <t>Western Asia</t>
         </is>
       </c>
       <c r="G139" s="0">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row outlineLevel="0" r="140">
       <c r="A140" s="0" t="inlineStr">
         <is>
-          <t>Czechia</t>
+          <t>Belarus</t>
         </is>
       </c>
       <c r="B140" s="0" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="C140" s="0">
-        <v>203</v>
+        <v>112</v>
       </c>
       <c r="D140" s="0" t="inlineStr">
         <is>
@@ -4695,16 +4695,16 @@
     <row outlineLevel="0" r="141">
       <c r="A141" s="0" t="inlineStr">
         <is>
-          <t>Czechoslovakia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
       <c r="B141" s="0" t="inlineStr">
         <is>
-          <t>CZSV</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="C141" s="0">
-        <v>203</v>
+        <v>100</v>
       </c>
       <c r="D141" s="0" t="inlineStr">
         <is>
@@ -4726,16 +4726,16 @@
     <row outlineLevel="0" r="142">
       <c r="A142" s="0" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Czechia</t>
         </is>
       </c>
       <c r="B142" s="0" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="C142" s="0">
-        <v>348</v>
+        <v>203</v>
       </c>
       <c r="D142" s="0" t="inlineStr">
         <is>
@@ -4757,16 +4757,16 @@
     <row outlineLevel="0" r="143">
       <c r="A143" s="0" t="inlineStr">
         <is>
-          <t>Moldova</t>
+          <t>Czechoslovakia</t>
         </is>
       </c>
       <c r="B143" s="0" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>CZSV</t>
         </is>
       </c>
       <c r="C143" s="0">
-        <v>498</v>
+        <v>203</v>
       </c>
       <c r="D143" s="0" t="inlineStr">
         <is>
@@ -4788,16 +4788,16 @@
     <row outlineLevel="0" r="144">
       <c r="A144" s="0" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="B144" s="0" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="C144" s="0">
-        <v>616</v>
+        <v>348</v>
       </c>
       <c r="D144" s="0" t="inlineStr">
         <is>
@@ -4819,16 +4819,16 @@
     <row outlineLevel="0" r="145">
       <c r="A145" s="0" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Moldova</t>
         </is>
       </c>
       <c r="B145" s="0" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="C145" s="0">
-        <v>642</v>
+        <v>498</v>
       </c>
       <c r="D145" s="0" t="inlineStr">
         <is>
@@ -4850,16 +4850,16 @@
     <row outlineLevel="0" r="146">
       <c r="A146" s="0" t="inlineStr">
         <is>
-          <t>Russia</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="B146" s="0" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="C146" s="0">
-        <v>643</v>
+        <v>616</v>
       </c>
       <c r="D146" s="0" t="inlineStr">
         <is>
@@ -4881,16 +4881,16 @@
     <row outlineLevel="0" r="147">
       <c r="A147" s="0" t="inlineStr">
         <is>
-          <t>Slovakia</t>
+          <t>Romania</t>
         </is>
       </c>
       <c r="B147" s="0" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="C147" s="0">
-        <v>703</v>
+        <v>642</v>
       </c>
       <c r="D147" s="0" t="inlineStr">
         <is>
@@ -4912,16 +4912,16 @@
     <row outlineLevel="0" r="148">
       <c r="A148" s="0" t="inlineStr">
         <is>
-          <t>Ukraine</t>
+          <t>Russia</t>
         </is>
       </c>
       <c r="B148" s="0" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="C148" s="0">
-        <v>804</v>
+        <v>643</v>
       </c>
       <c r="D148" s="0" t="inlineStr">
         <is>
@@ -4943,16 +4943,16 @@
     <row outlineLevel="0" r="149">
       <c r="A149" s="0" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B149" s="0" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="C149" s="0">
-        <v>208</v>
+        <v>703</v>
       </c>
       <c r="D149" s="0" t="inlineStr">
         <is>
@@ -4964,26 +4964,26 @@
       </c>
       <c r="F149" s="0" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="G149" s="0">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row outlineLevel="0" r="150">
       <c r="A150" s="0" t="inlineStr">
         <is>
-          <t>England and Wales</t>
+          <t>Ukraine</t>
         </is>
       </c>
       <c r="B150" s="0" t="inlineStr">
         <is>
-          <t>ENGWAL</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="C150" s="0">
-        <v>826</v>
+        <v>804</v>
       </c>
       <c r="D150" s="0" t="inlineStr">
         <is>
@@ -4995,26 +4995,26 @@
       </c>
       <c r="F150" s="0" t="inlineStr">
         <is>
-          <t>Northern Europe</t>
+          <t>Eastern Europe</t>
         </is>
       </c>
       <c r="G150" s="0">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row outlineLevel="0" r="151">
       <c r="A151" s="0" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
       <c r="B151" s="0" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="C151" s="0">
-        <v>233</v>
+        <v>208</v>
       </c>
       <c r="D151" s="0" t="inlineStr">
         <is>
@@ -5036,16 +5036,16 @@
     <row outlineLevel="0" r="152">
       <c r="A152" s="0" t="inlineStr">
         <is>
-          <t>Faroe Islands</t>
+          <t>England and Wales</t>
         </is>
       </c>
       <c r="B152" s="0" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>ENGWAL</t>
         </is>
       </c>
       <c r="C152" s="0">
-        <v>234</v>
+        <v>826</v>
       </c>
       <c r="D152" s="0" t="inlineStr">
         <is>
@@ -5067,16 +5067,16 @@
     <row outlineLevel="0" r="153">
       <c r="A153" s="0" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="B153" s="0" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="C153" s="0">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="D153" s="0" t="inlineStr">
         <is>
@@ -5098,16 +5098,16 @@
     <row outlineLevel="0" r="154">
       <c r="A154" s="0" t="inlineStr">
         <is>
-          <t>Guernsey</t>
+          <t>Faroe Islands</t>
         </is>
       </c>
       <c r="B154" s="0" t="inlineStr">
         <is>
-          <t>GGY</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="C154" s="0">
-        <v>831</v>
+        <v>234</v>
       </c>
       <c r="D154" s="0" t="inlineStr">
         <is>
@@ -5129,16 +5129,16 @@
     <row outlineLevel="0" r="155">
       <c r="A155" s="0" t="inlineStr">
         <is>
-          <t>Iceland</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="B155" s="0" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="C155" s="0">
-        <v>352</v>
+        <v>246</v>
       </c>
       <c r="D155" s="0" t="inlineStr">
         <is>
@@ -5160,16 +5160,16 @@
     <row outlineLevel="0" r="156">
       <c r="A156" s="0" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Guernsey</t>
         </is>
       </c>
       <c r="B156" s="0" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>GGY</t>
         </is>
       </c>
       <c r="C156" s="0">
-        <v>372</v>
+        <v>831</v>
       </c>
       <c r="D156" s="0" t="inlineStr">
         <is>
@@ -5191,16 +5191,16 @@
     <row outlineLevel="0" r="157">
       <c r="A157" s="0" t="inlineStr">
         <is>
-          <t>Isle of Man</t>
+          <t>Iceland</t>
         </is>
       </c>
       <c r="B157" s="0" t="inlineStr">
         <is>
-          <t>IMN</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="C157" s="0">
-        <v>833</v>
+        <v>352</v>
       </c>
       <c r="D157" s="0" t="inlineStr">
         <is>
@@ -5222,16 +5222,16 @@
     <row outlineLevel="0" r="158">
       <c r="A158" s="0" t="inlineStr">
         <is>
-          <t>Jersey</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B158" s="0" t="inlineStr">
         <is>
-          <t>JEY</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="C158" s="0">
-        <v>832</v>
+        <v>372</v>
       </c>
       <c r="D158" s="0" t="inlineStr">
         <is>
@@ -5253,16 +5253,16 @@
     <row outlineLevel="0" r="159">
       <c r="A159" s="0" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Isle of Man</t>
         </is>
       </c>
       <c r="B159" s="0" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>IMN</t>
         </is>
       </c>
       <c r="C159" s="0">
-        <v>428</v>
+        <v>833</v>
       </c>
       <c r="D159" s="0" t="inlineStr">
         <is>
@@ -5284,16 +5284,16 @@
     <row outlineLevel="0" r="160">
       <c r="A160" s="0" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Jersey</t>
         </is>
       </c>
       <c r="B160" s="0" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>JEY</t>
         </is>
       </c>
       <c r="C160" s="0">
-        <v>440</v>
+        <v>832</v>
       </c>
       <c r="D160" s="0" t="inlineStr">
         <is>
@@ -5315,16 +5315,16 @@
     <row outlineLevel="0" r="161">
       <c r="A161" s="0" t="inlineStr">
         <is>
-          <t>Northern Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B161" s="0" t="inlineStr">
         <is>
-          <t>NORIRE</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="C161" s="0">
-        <v>826</v>
+        <v>428</v>
       </c>
       <c r="D161" s="0" t="inlineStr">
         <is>
@@ -5346,16 +5346,16 @@
     <row outlineLevel="0" r="162">
       <c r="A162" s="0" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B162" s="0" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="C162" s="0">
-        <v>578</v>
+        <v>440</v>
       </c>
       <c r="D162" s="0" t="inlineStr">
         <is>
@@ -5377,12 +5377,12 @@
     <row outlineLevel="0" r="163">
       <c r="A163" s="0" t="inlineStr">
         <is>
-          <t>Scotland</t>
+          <t>Northern Ireland</t>
         </is>
       </c>
       <c r="B163" s="0" t="inlineStr">
         <is>
-          <t>SCOT</t>
+          <t>NORIRE</t>
         </is>
       </c>
       <c r="C163" s="0">
@@ -5408,16 +5408,16 @@
     <row outlineLevel="0" r="164">
       <c r="A164" s="0" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="B164" s="0" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="C164" s="0">
-        <v>752</v>
+        <v>578</v>
       </c>
       <c r="D164" s="0" t="inlineStr">
         <is>
@@ -5439,12 +5439,12 @@
     <row outlineLevel="0" r="165">
       <c r="A165" s="0" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Scotland</t>
         </is>
       </c>
       <c r="B165" s="0" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>SCOT</t>
         </is>
       </c>
       <c r="C165" s="0">
@@ -5470,16 +5470,16 @@
     <row outlineLevel="0" r="166">
       <c r="A166" s="0" t="inlineStr">
         <is>
-          <t>Albania</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="B166" s="0" t="inlineStr">
         <is>
-          <t>ALB</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="C166" s="0">
-        <v>8</v>
+        <v>752</v>
       </c>
       <c r="D166" s="0" t="inlineStr">
         <is>
@@ -5491,26 +5491,26 @@
       </c>
       <c r="F166" s="0" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="G166" s="0">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row outlineLevel="0" r="167">
       <c r="A167" s="0" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="B167" s="0" t="inlineStr">
         <is>
-          <t>AND</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="C167" s="0">
-        <v>20</v>
+        <v>826</v>
       </c>
       <c r="D167" s="0" t="inlineStr">
         <is>
@@ -5522,26 +5522,26 @@
       </c>
       <c r="F167" s="0" t="inlineStr">
         <is>
-          <t>Southern Europe</t>
+          <t>Northern Europe</t>
         </is>
       </c>
       <c r="G167" s="0">
-        <v>39</v>
+        <v>154</v>
       </c>
     </row>
     <row outlineLevel="0" r="168">
       <c r="A168" s="0" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina</t>
+          <t>Albania</t>
         </is>
       </c>
       <c r="B168" s="0" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>ALB</t>
         </is>
       </c>
       <c r="C168" s="0">
-        <v>70</v>
+        <v>8</v>
       </c>
       <c r="D168" s="0" t="inlineStr">
         <is>
@@ -5563,16 +5563,16 @@
     <row outlineLevel="0" r="169">
       <c r="A169" s="0" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="B169" s="0" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>AND</t>
         </is>
       </c>
       <c r="C169" s="0">
-        <v>191</v>
+        <v>20</v>
       </c>
       <c r="D169" s="0" t="inlineStr">
         <is>
@@ -5594,16 +5594,16 @@
     <row outlineLevel="0" r="170">
       <c r="A170" s="0" t="inlineStr">
         <is>
-          <t>Gibraltar</t>
+          <t>Bosnia and Herzegovina</t>
         </is>
       </c>
       <c r="B170" s="0" t="inlineStr">
         <is>
-          <t>GIB</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="C170" s="0">
-        <v>292</v>
+        <v>70</v>
       </c>
       <c r="D170" s="0" t="inlineStr">
         <is>
@@ -5625,16 +5625,16 @@
     <row outlineLevel="0" r="171">
       <c r="A171" s="0" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Croatia</t>
         </is>
       </c>
       <c r="B171" s="0" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="C171" s="0">
-        <v>300</v>
+        <v>191</v>
       </c>
       <c r="D171" s="0" t="inlineStr">
         <is>
@@ -5656,16 +5656,16 @@
     <row outlineLevel="0" r="172">
       <c r="A172" s="0" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Gibraltar</t>
         </is>
       </c>
       <c r="B172" s="0" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>GIB</t>
         </is>
       </c>
       <c r="C172" s="0">
-        <v>380</v>
+        <v>292</v>
       </c>
       <c r="D172" s="0" t="inlineStr">
         <is>
@@ -5687,15 +5687,17 @@
     <row outlineLevel="0" r="173">
       <c r="A173" s="0" t="inlineStr">
         <is>
-          <t>Kosovo</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="B173" s="0" t="inlineStr">
         <is>
-          <t>XKX</t>
-        </is>
-      </c>
-      <c r="C173" s="0"/>
+          <t>GRC</t>
+        </is>
+      </c>
+      <c r="C173" s="0">
+        <v>300</v>
+      </c>
       <c r="D173" s="0" t="inlineStr">
         <is>
           <t>Europe</t>
@@ -5716,16 +5718,16 @@
     <row outlineLevel="0" r="174">
       <c r="A174" s="0" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="B174" s="0" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C174" s="0">
-        <v>470</v>
+        <v>380</v>
       </c>
       <c r="D174" s="0" t="inlineStr">
         <is>
@@ -5747,16 +5749,13 @@
     <row outlineLevel="0" r="175">
       <c r="A175" s="0" t="inlineStr">
         <is>
-          <t>Montenegro</t>
+          <t>Kosovo</t>
         </is>
       </c>
       <c r="B175" s="0" t="inlineStr">
         <is>
-          <t>MNE</t>
-        </is>
-      </c>
-      <c r="C175" s="0">
-        <v>499</v>
+          <t>XKX</t>
+        </is>
       </c>
       <c r="D175" s="0" t="inlineStr">
         <is>
@@ -5778,16 +5777,16 @@
     <row outlineLevel="0" r="176">
       <c r="A176" s="0" t="inlineStr">
         <is>
-          <t>North Macedonia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B176" s="0" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="C176" s="0">
-        <v>807</v>
+        <v>470</v>
       </c>
       <c r="D176" s="0" t="inlineStr">
         <is>
@@ -5809,16 +5808,16 @@
     <row outlineLevel="0" r="177">
       <c r="A177" s="0" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Montenegro</t>
         </is>
       </c>
       <c r="B177" s="0" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="C177" s="0">
-        <v>620</v>
+        <v>499</v>
       </c>
       <c r="D177" s="0" t="inlineStr">
         <is>
@@ -5840,16 +5839,16 @@
     <row outlineLevel="0" r="178">
       <c r="A178" s="0" t="inlineStr">
         <is>
-          <t>San Marino</t>
+          <t>North Macedonia</t>
         </is>
       </c>
       <c r="B178" s="0" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="C178" s="0">
-        <v>674</v>
+        <v>807</v>
       </c>
       <c r="D178" s="0" t="inlineStr">
         <is>
@@ -5871,16 +5870,16 @@
     <row outlineLevel="0" r="179">
       <c r="A179" s="0" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="B179" s="0" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="C179" s="0">
-        <v>688</v>
+        <v>620</v>
       </c>
       <c r="D179" s="0" t="inlineStr">
         <is>
@@ -5902,16 +5901,16 @@
     <row outlineLevel="0" r="180">
       <c r="A180" s="0" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>San Marino</t>
         </is>
       </c>
       <c r="B180" s="0" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="C180" s="0">
-        <v>705</v>
+        <v>674</v>
       </c>
       <c r="D180" s="0" t="inlineStr">
         <is>
@@ -5933,16 +5932,16 @@
     <row outlineLevel="0" r="181">
       <c r="A181" s="0" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="B181" s="0" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="C181" s="0">
-        <v>724</v>
+        <v>688</v>
       </c>
       <c r="D181" s="0" t="inlineStr">
         <is>
@@ -5964,16 +5963,16 @@
     <row outlineLevel="0" r="182">
       <c r="A182" s="0" t="inlineStr">
         <is>
-          <t>Yugoslavia</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B182" s="0" t="inlineStr">
         <is>
-          <t>YUGI</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="C182" s="0">
-        <v>688</v>
+        <v>705</v>
       </c>
       <c r="D182" s="0" t="inlineStr">
         <is>
@@ -5995,16 +5994,16 @@
     <row outlineLevel="0" r="183">
       <c r="A183" s="0" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="B183" s="0" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="C183" s="0">
-        <v>40</v>
+        <v>724</v>
       </c>
       <c r="D183" s="0" t="inlineStr">
         <is>
@@ -6016,26 +6015,26 @@
       </c>
       <c r="F183" s="0" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="G183" s="0">
-        <v>155</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="184">
       <c r="A184" s="0" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Yugoslavia</t>
         </is>
       </c>
       <c r="B184" s="0" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>YUGI</t>
         </is>
       </c>
       <c r="C184" s="0">
-        <v>56</v>
+        <v>688</v>
       </c>
       <c r="D184" s="0" t="inlineStr">
         <is>
@@ -6047,26 +6046,26 @@
       </c>
       <c r="F184" s="0" t="inlineStr">
         <is>
-          <t>Western Europe</t>
+          <t>Southern Europe</t>
         </is>
       </c>
       <c r="G184" s="0">
-        <v>155</v>
+        <v>39</v>
       </c>
     </row>
     <row outlineLevel="0" r="185">
       <c r="A185" s="0" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Austria</t>
         </is>
       </c>
       <c r="B185" s="0" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="C185" s="0">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="D185" s="0" t="inlineStr">
         <is>
@@ -6088,16 +6087,16 @@
     <row outlineLevel="0" r="186">
       <c r="A186" s="0" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="B186" s="0" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="C186" s="0">
-        <v>276</v>
+        <v>56</v>
       </c>
       <c r="D186" s="0" t="inlineStr">
         <is>
@@ -6119,16 +6118,16 @@
     <row outlineLevel="0" r="187">
       <c r="A187" s="0" t="inlineStr">
         <is>
-          <t>Liechtenstein</t>
+          <t>France</t>
         </is>
       </c>
       <c r="B187" s="0" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="C187" s="0">
-        <v>438</v>
+        <v>250</v>
       </c>
       <c r="D187" s="0" t="inlineStr">
         <is>
@@ -6150,16 +6149,16 @@
     <row outlineLevel="0" r="188">
       <c r="A188" s="0" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="B188" s="0" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="C188" s="0">
-        <v>442</v>
+        <v>276</v>
       </c>
       <c r="D188" s="0" t="inlineStr">
         <is>
@@ -6181,16 +6180,16 @@
     <row outlineLevel="0" r="189">
       <c r="A189" s="0" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Liechtenstein</t>
         </is>
       </c>
       <c r="B189" s="0" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>LIE</t>
         </is>
       </c>
       <c r="C189" s="0">
-        <v>492</v>
+        <v>438</v>
       </c>
       <c r="D189" s="0" t="inlineStr">
         <is>
@@ -6212,16 +6211,16 @@
     <row outlineLevel="0" r="190">
       <c r="A190" s="0" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B190" s="0" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="C190" s="0">
-        <v>528</v>
+        <v>442</v>
       </c>
       <c r="D190" s="0" t="inlineStr">
         <is>
@@ -6243,16 +6242,16 @@
     <row outlineLevel="0" r="191">
       <c r="A191" s="0" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="B191" s="0" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="C191" s="0">
-        <v>756</v>
+        <v>492</v>
       </c>
       <c r="D191" s="0" t="inlineStr">
         <is>
@@ -6274,78 +6273,78 @@
     <row outlineLevel="0" r="192">
       <c r="A192" s="0" t="inlineStr">
         <is>
-          <t>Bermuda</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="B192" s="0" t="inlineStr">
         <is>
-          <t>BMU</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="C192" s="0">
-        <v>60</v>
+        <v>528</v>
       </c>
       <c r="D192" s="0" t="inlineStr">
         <is>
-          <t>Northern America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E192" s="0">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="F192" s="0" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="G192" s="0">
-        <v>22</v>
+        <v>155</v>
       </c>
     </row>
     <row outlineLevel="0" r="193">
       <c r="A193" s="0" t="inlineStr">
         <is>
-          <t>Greenland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="B193" s="0" t="inlineStr">
         <is>
-          <t>GRL</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="C193" s="0">
-        <v>304</v>
+        <v>756</v>
       </c>
       <c r="D193" s="0" t="inlineStr">
         <is>
-          <t>Northern America</t>
+          <t>Europe</t>
         </is>
       </c>
       <c r="E193" s="0">
-        <v>119</v>
+        <v>150</v>
       </c>
       <c r="F193" s="0" t="inlineStr">
         <is>
-          <t>Islands</t>
+          <t>Western Europe</t>
         </is>
       </c>
       <c r="G193" s="0">
-        <v>22</v>
+        <v>155</v>
       </c>
     </row>
     <row outlineLevel="0" r="194">
       <c r="A194" s="0" t="inlineStr">
         <is>
-          <t>Saint Pierre and Miquelon</t>
+          <t>Bermuda</t>
         </is>
       </c>
       <c r="B194" s="0" t="inlineStr">
         <is>
-          <t>SPM</t>
+          <t>BMU</t>
         </is>
       </c>
       <c r="C194" s="0">
-        <v>666</v>
+        <v>60</v>
       </c>
       <c r="D194" s="0" t="inlineStr">
         <is>
@@ -6367,16 +6366,16 @@
     <row outlineLevel="0" r="195">
       <c r="A195" s="0" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Greenland</t>
         </is>
       </c>
       <c r="B195" s="0" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>GRL</t>
         </is>
       </c>
       <c r="C195" s="0">
-        <v>124</v>
+        <v>304</v>
       </c>
       <c r="D195" s="0" t="inlineStr">
         <is>
@@ -6388,26 +6387,26 @@
       </c>
       <c r="F195" s="0" t="inlineStr">
         <is>
-          <t>US &amp; Canada</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="G195" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="196">
       <c r="A196" s="0" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Saint Pierre and Miquelon</t>
         </is>
       </c>
       <c r="B196" s="0" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>SPM</t>
         </is>
       </c>
       <c r="C196" s="0">
-        <v>840</v>
+        <v>666</v>
       </c>
       <c r="D196" s="0" t="inlineStr">
         <is>
@@ -6419,88 +6418,88 @@
       </c>
       <c r="F196" s="0" t="inlineStr">
         <is>
-          <t>US &amp; Canada</t>
+          <t>Islands</t>
         </is>
       </c>
       <c r="G196" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row outlineLevel="0" r="197">
       <c r="A197" s="0" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="B197" s="0" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C197" s="0">
-        <v>36</v>
+        <v>124</v>
       </c>
       <c r="D197" s="0" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Northern America</t>
         </is>
       </c>
       <c r="E197" s="0">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="F197" s="0" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>US &amp; Canada</t>
         </is>
       </c>
       <c r="G197" s="0">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="198">
       <c r="A198" s="0" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="B198" s="0" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="C198" s="0">
-        <v>554</v>
+        <v>840</v>
       </c>
       <c r="D198" s="0" t="inlineStr">
         <is>
-          <t>Oceania</t>
+          <t>Northern America</t>
         </is>
       </c>
       <c r="E198" s="0">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="F198" s="0" t="inlineStr">
         <is>
-          <t>Australia and New Zealand</t>
+          <t>US &amp; Canada</t>
         </is>
       </c>
       <c r="G198" s="0">
-        <v>53</v>
+        <v>21</v>
       </c>
     </row>
     <row outlineLevel="0" r="199">
       <c r="A199" s="0" t="inlineStr">
         <is>
-          <t>Fiji</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B199" s="0" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="C199" s="0">
-        <v>242</v>
+        <v>36</v>
       </c>
       <c r="D199" s="0" t="inlineStr">
         <is>
@@ -6512,26 +6511,26 @@
       </c>
       <c r="F199" s="0" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="G199" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row outlineLevel="0" r="200">
       <c r="A200" s="0" t="inlineStr">
         <is>
-          <t>New Caledonia</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="B200" s="0" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="C200" s="0">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="D200" s="0" t="inlineStr">
         <is>
@@ -6543,26 +6542,26 @@
       </c>
       <c r="F200" s="0" t="inlineStr">
         <is>
-          <t>Melanesia</t>
+          <t>Australia and New Zealand</t>
         </is>
       </c>
       <c r="G200" s="0">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row outlineLevel="0" r="201">
       <c r="A201" s="0" t="inlineStr">
         <is>
-          <t>Papua New Guinea</t>
+          <t>Fiji</t>
         </is>
       </c>
       <c r="B201" s="0" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="C201" s="0">
-        <v>598</v>
+        <v>242</v>
       </c>
       <c r="D201" s="0" t="inlineStr">
         <is>
@@ -6584,16 +6583,16 @@
     <row outlineLevel="0" r="202">
       <c r="A202" s="0" t="inlineStr">
         <is>
-          <t>Solomon Islands</t>
+          <t>New Caledonia</t>
         </is>
       </c>
       <c r="B202" s="0" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>NCL</t>
         </is>
       </c>
       <c r="C202" s="0">
-        <v>90</v>
+        <v>540</v>
       </c>
       <c r="D202" s="0" t="inlineStr">
         <is>
@@ -6615,16 +6614,16 @@
     <row outlineLevel="0" r="203">
       <c r="A203" s="0" t="inlineStr">
         <is>
-          <t>Vanuatu</t>
+          <t>Papua New Guinea</t>
         </is>
       </c>
       <c r="B203" s="0" t="inlineStr">
         <is>
-          <t>VUT</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="C203" s="0">
-        <v>548</v>
+        <v>598</v>
       </c>
       <c r="D203" s="0" t="inlineStr">
         <is>
@@ -6646,16 +6645,16 @@
     <row outlineLevel="0" r="204">
       <c r="A204" s="0" t="inlineStr">
         <is>
-          <t>Guam</t>
+          <t>Solomon Islands</t>
         </is>
       </c>
       <c r="B204" s="0" t="inlineStr">
         <is>
-          <t>GUM</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C204" s="0">
-        <v>316</v>
+        <v>90</v>
       </c>
       <c r="D204" s="0" t="inlineStr">
         <is>
@@ -6667,26 +6666,26 @@
       </c>
       <c r="F204" s="0" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="G204" s="0">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row outlineLevel="0" r="205">
       <c r="A205" s="0" t="inlineStr">
         <is>
-          <t>Kiribati</t>
+          <t>Vanuatu</t>
         </is>
       </c>
       <c r="B205" s="0" t="inlineStr">
         <is>
-          <t>KIR</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="C205" s="0">
-        <v>296</v>
+        <v>548</v>
       </c>
       <c r="D205" s="0" t="inlineStr">
         <is>
@@ -6698,26 +6697,26 @@
       </c>
       <c r="F205" s="0" t="inlineStr">
         <is>
-          <t>Micronesia</t>
+          <t>Melanesia</t>
         </is>
       </c>
       <c r="G205" s="0">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row outlineLevel="0" r="206">
       <c r="A206" s="0" t="inlineStr">
         <is>
-          <t>Marshall Islands</t>
+          <t>Guam</t>
         </is>
       </c>
       <c r="B206" s="0" t="inlineStr">
         <is>
-          <t>MHL</t>
+          <t>GUM</t>
         </is>
       </c>
       <c r="C206" s="0">
-        <v>584</v>
+        <v>316</v>
       </c>
       <c r="D206" s="0" t="inlineStr">
         <is>
@@ -6739,16 +6738,16 @@
     <row outlineLevel="0" r="207">
       <c r="A207" s="0" t="inlineStr">
         <is>
-          <t>Micronesia Fed</t>
+          <t>Kiribati</t>
         </is>
       </c>
       <c r="B207" s="0" t="inlineStr">
         <is>
-          <t>FSM</t>
+          <t>KIR</t>
         </is>
       </c>
       <c r="C207" s="0">
-        <v>583</v>
+        <v>296</v>
       </c>
       <c r="D207" s="0" t="inlineStr">
         <is>
@@ -6770,16 +6769,16 @@
     <row outlineLevel="0" r="208">
       <c r="A208" s="0" t="inlineStr">
         <is>
-          <t>Nauru</t>
+          <t>Marshall Islands</t>
         </is>
       </c>
       <c r="B208" s="0" t="inlineStr">
         <is>
-          <t>NRU</t>
+          <t>MHL</t>
         </is>
       </c>
       <c r="C208" s="0">
-        <v>520</v>
+        <v>584</v>
       </c>
       <c r="D208" s="0" t="inlineStr">
         <is>
@@ -6801,16 +6800,16 @@
     <row outlineLevel="0" r="209">
       <c r="A209" s="0" t="inlineStr">
         <is>
-          <t>Northern Mariana Islands</t>
+          <t>Micronesia Fed</t>
         </is>
       </c>
       <c r="B209" s="0" t="inlineStr">
         <is>
-          <t>MNP</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="C209" s="0">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D209" s="0" t="inlineStr">
         <is>
@@ -6832,16 +6831,16 @@
     <row outlineLevel="0" r="210">
       <c r="A210" s="0" t="inlineStr">
         <is>
-          <t>Palau</t>
+          <t>Nauru</t>
         </is>
       </c>
       <c r="B210" s="0" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>NRU</t>
         </is>
       </c>
       <c r="C210" s="0">
-        <v>585</v>
+        <v>520</v>
       </c>
       <c r="D210" s="0" t="inlineStr">
         <is>
@@ -6863,16 +6862,16 @@
     <row outlineLevel="0" r="211">
       <c r="A211" s="0" t="inlineStr">
         <is>
-          <t>American Samoa</t>
+          <t>Northern Mariana Islands</t>
         </is>
       </c>
       <c r="B211" s="0" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>MNP</t>
         </is>
       </c>
       <c r="C211" s="0">
-        <v>16</v>
+        <v>580</v>
       </c>
       <c r="D211" s="0" t="inlineStr">
         <is>
@@ -6884,26 +6883,26 @@
       </c>
       <c r="F211" s="0" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="G211" s="0">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row outlineLevel="0" r="212">
       <c r="A212" s="0" t="inlineStr">
         <is>
-          <t>Cook Islands</t>
+          <t>Palau</t>
         </is>
       </c>
       <c r="B212" s="0" t="inlineStr">
         <is>
-          <t>COK</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="C212" s="0">
-        <v>184</v>
+        <v>585</v>
       </c>
       <c r="D212" s="0" t="inlineStr">
         <is>
@@ -6915,26 +6914,26 @@
       </c>
       <c r="F212" s="0" t="inlineStr">
         <is>
-          <t>Polynesia</t>
+          <t>Micronesia</t>
         </is>
       </c>
       <c r="G212" s="0">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row outlineLevel="0" r="213">
       <c r="A213" s="0" t="inlineStr">
         <is>
-          <t>French Polynesia</t>
+          <t>American Samoa</t>
         </is>
       </c>
       <c r="B213" s="0" t="inlineStr">
         <is>
-          <t>PYF</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="C213" s="0">
-        <v>258</v>
+        <v>16</v>
       </c>
       <c r="D213" s="0" t="inlineStr">
         <is>
@@ -6956,16 +6955,16 @@
     <row outlineLevel="0" r="214">
       <c r="A214" s="0" t="inlineStr">
         <is>
-          <t>Samoa</t>
+          <t>Cook Islands</t>
         </is>
       </c>
       <c r="B214" s="0" t="inlineStr">
         <is>
-          <t>WSM</t>
+          <t>COK</t>
         </is>
       </c>
       <c r="C214" s="0">
-        <v>882</v>
+        <v>184</v>
       </c>
       <c r="D214" s="0" t="inlineStr">
         <is>
@@ -6987,16 +6986,16 @@
     <row outlineLevel="0" r="215">
       <c r="A215" s="0" t="inlineStr">
         <is>
-          <t>Tonga</t>
+          <t>French Polynesia</t>
         </is>
       </c>
       <c r="B215" s="0" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>PYF</t>
         </is>
       </c>
       <c r="C215" s="0">
-        <v>776</v>
+        <v>258</v>
       </c>
       <c r="D215" s="0" t="inlineStr">
         <is>
@@ -7018,16 +7017,16 @@
     <row outlineLevel="0" r="216">
       <c r="A216" s="0" t="inlineStr">
         <is>
-          <t>Tuvalu</t>
+          <t>Samoa</t>
         </is>
       </c>
       <c r="B216" s="0" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="C216" s="0">
-        <v>798</v>
+        <v>882</v>
       </c>
       <c r="D216" s="0" t="inlineStr">
         <is>
@@ -7049,16 +7048,16 @@
     <row outlineLevel="0" r="217">
       <c r="A217" s="0" t="inlineStr">
         <is>
-          <t>Wallis and Futuna</t>
+          <t>Tonga</t>
         </is>
       </c>
       <c r="B217" s="0" t="inlineStr">
         <is>
-          <t>WLF</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="C217" s="0">
-        <v>876</v>
+        <v>776</v>
       </c>
       <c r="D217" s="0" t="inlineStr">
         <is>
@@ -7080,78 +7079,78 @@
     <row outlineLevel="0" r="218">
       <c r="A218" s="0" t="inlineStr">
         <is>
-          <t>Bolivia</t>
+          <t>Tuvalu</t>
         </is>
       </c>
       <c r="B218" s="0" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="C218" s="0">
-        <v>68</v>
+        <v>798</v>
       </c>
       <c r="D218" s="0" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="E218" s="0">
-        <v>219</v>
+        <v>9</v>
       </c>
       <c r="F218" s="0" t="inlineStr">
         <is>
-          <t>Andean &amp; Amazonian</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="G218" s="0">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row outlineLevel="0" r="219">
       <c r="A219" s="0" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Wallis and Futuna</t>
         </is>
       </c>
       <c r="B219" s="0" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>WLF</t>
         </is>
       </c>
       <c r="C219" s="0">
-        <v>76</v>
+        <v>876</v>
       </c>
       <c r="D219" s="0" t="inlineStr">
         <is>
-          <t>South America</t>
+          <t>Oceania</t>
         </is>
       </c>
       <c r="E219" s="0">
-        <v>219</v>
+        <v>9</v>
       </c>
       <c r="F219" s="0" t="inlineStr">
         <is>
-          <t>Andean &amp; Amazonian</t>
+          <t>Polynesia</t>
         </is>
       </c>
       <c r="G219" s="0">
-        <v>5</v>
+        <v>61</v>
       </c>
     </row>
     <row outlineLevel="0" r="220">
       <c r="A220" s="0" t="inlineStr">
         <is>
-          <t>Colombia</t>
+          <t>Bolivia</t>
         </is>
       </c>
       <c r="B220" s="0" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="C220" s="0">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="D220" s="0" t="inlineStr">
         <is>
@@ -7173,16 +7172,16 @@
     <row outlineLevel="0" r="221">
       <c r="A221" s="0" t="inlineStr">
         <is>
-          <t>Ecuador</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="B221" s="0" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="C221" s="0">
-        <v>218</v>
+        <v>76</v>
       </c>
       <c r="D221" s="0" t="inlineStr">
         <is>
@@ -7204,16 +7203,16 @@
     <row outlineLevel="0" r="222">
       <c r="A222" s="0" t="inlineStr">
         <is>
-          <t>Guyana</t>
+          <t>Colombia</t>
         </is>
       </c>
       <c r="B222" s="0" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="C222" s="0">
-        <v>328</v>
+        <v>170</v>
       </c>
       <c r="D222" s="0" t="inlineStr">
         <is>
@@ -7235,16 +7234,16 @@
     <row outlineLevel="0" r="223">
       <c r="A223" s="0" t="inlineStr">
         <is>
-          <t>Paraguay</t>
+          <t>Ecuador</t>
         </is>
       </c>
       <c r="B223" s="0" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="C223" s="0">
-        <v>600</v>
+        <v>218</v>
       </c>
       <c r="D223" s="0" t="inlineStr">
         <is>
@@ -7266,16 +7265,16 @@
     <row outlineLevel="0" r="224">
       <c r="A224" s="0" t="inlineStr">
         <is>
-          <t>Peru</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="B224" s="0" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="C224" s="0">
-        <v>604</v>
+        <v>328</v>
       </c>
       <c r="D224" s="0" t="inlineStr">
         <is>
@@ -7297,16 +7296,16 @@
     <row outlineLevel="0" r="225">
       <c r="A225" s="0" t="inlineStr">
         <is>
-          <t>Suriname</t>
+          <t>Paraguay</t>
         </is>
       </c>
       <c r="B225" s="0" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="C225" s="0">
-        <v>740</v>
+        <v>600</v>
       </c>
       <c r="D225" s="0" t="inlineStr">
         <is>
@@ -7328,16 +7327,16 @@
     <row outlineLevel="0" r="226">
       <c r="A226" s="0" t="inlineStr">
         <is>
-          <t>Venezuela</t>
+          <t>Peru</t>
         </is>
       </c>
       <c r="B226" s="0" t="inlineStr">
         <is>
-          <t>VEN</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="C226" s="0">
-        <v>862</v>
+        <v>604</v>
       </c>
       <c r="D226" s="0" t="inlineStr">
         <is>
@@ -7359,16 +7358,16 @@
     <row outlineLevel="0" r="227">
       <c r="A227" s="0" t="inlineStr">
         <is>
-          <t>Argentina</t>
+          <t>Suriname</t>
         </is>
       </c>
       <c r="B227" s="0" t="inlineStr">
         <is>
-          <t>ARG</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="C227" s="0">
-        <v>32</v>
+        <v>740</v>
       </c>
       <c r="D227" s="0" t="inlineStr">
         <is>
@@ -7380,26 +7379,26 @@
       </c>
       <c r="F227" s="0" t="inlineStr">
         <is>
-          <t>Southern Cone</t>
+          <t>Andean &amp; Amazonian</t>
         </is>
       </c>
       <c r="G227" s="0">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="228">
       <c r="A228" s="0" t="inlineStr">
         <is>
-          <t>Chile</t>
+          <t>Venezuela</t>
         </is>
       </c>
       <c r="B228" s="0" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>VEN</t>
         </is>
       </c>
       <c r="C228" s="0">
-        <v>152</v>
+        <v>862</v>
       </c>
       <c r="D228" s="0" t="inlineStr">
         <is>
@@ -7411,26 +7410,26 @@
       </c>
       <c r="F228" s="0" t="inlineStr">
         <is>
-          <t>Southern Cone</t>
+          <t>Andean &amp; Amazonian</t>
         </is>
       </c>
       <c r="G228" s="0">
-        <v>105</v>
+        <v>5</v>
       </c>
     </row>
     <row outlineLevel="0" r="229">
       <c r="A229" s="0" t="inlineStr">
         <is>
-          <t>Uruguay</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="B229" s="0" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>ARG</t>
         </is>
       </c>
       <c r="C229" s="0">
-        <v>858</v>
+        <v>32</v>
       </c>
       <c r="D229" s="0" t="inlineStr">
         <is>
@@ -7450,40 +7449,66 @@
       </c>
     </row>
     <row outlineLevel="0" r="230">
-      <c r="A230" s="0" t="inlineStr"/>
-      <c r="B230" s="0" t="inlineStr"/>
-      <c r="C230" s="0"/>
-      <c r="D230" s="0" t="inlineStr"/>
-      <c r="E230" s="0"/>
-      <c r="F230" s="0" t="inlineStr"/>
-      <c r="G230" s="0"/>
+      <c r="A230" s="0" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="B230" s="0" t="inlineStr">
+        <is>
+          <t>CHL</t>
+        </is>
+      </c>
+      <c r="C230" s="0">
+        <v>152</v>
+      </c>
+      <c r="D230" s="0" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="E230" s="0">
+        <v>219</v>
+      </c>
+      <c r="F230" s="0" t="inlineStr">
+        <is>
+          <t>Southern Cone</t>
+        </is>
+      </c>
+      <c r="G230" s="0">
+        <v>105</v>
+      </c>
     </row>
     <row outlineLevel="0" r="231">
-      <c r="A231" s="0" t="inlineStr"/>
-      <c r="B231" s="0" t="inlineStr"/>
-      <c r="C231" s="0"/>
-      <c r="D231" s="0" t="inlineStr"/>
-      <c r="E231" s="0"/>
-      <c r="F231" s="0" t="inlineStr"/>
-      <c r="G231" s="0"/>
-    </row>
-    <row outlineLevel="0" r="232">
-      <c r="A232" s="0" t="inlineStr"/>
-      <c r="B232" s="0" t="inlineStr"/>
-      <c r="C232" s="0"/>
-      <c r="D232" s="0" t="inlineStr"/>
-      <c r="E232" s="0"/>
-      <c r="F232" s="0" t="inlineStr"/>
-      <c r="G232" s="0"/>
-    </row>
-    <row outlineLevel="0" r="233">
-      <c r="A233" s="0" t="inlineStr"/>
-      <c r="B233" s="0" t="inlineStr"/>
-      <c r="C233" s="0"/>
-      <c r="D233" s="0" t="inlineStr"/>
-      <c r="E233" s="0"/>
-      <c r="F233" s="0" t="inlineStr"/>
-      <c r="G233" s="0"/>
+      <c r="A231" s="0" t="inlineStr">
+        <is>
+          <t>Uruguay</t>
+        </is>
+      </c>
+      <c r="B231" s="0" t="inlineStr">
+        <is>
+          <t>URY</t>
+        </is>
+      </c>
+      <c r="C231" s="0">
+        <v>858</v>
+      </c>
+      <c r="D231" s="0" t="inlineStr">
+        <is>
+          <t>South America</t>
+        </is>
+      </c>
+      <c r="E231" s="0">
+        <v>219</v>
+      </c>
+      <c r="F231" s="0" t="inlineStr">
+        <is>
+          <t>Southern Cone</t>
+        </is>
+      </c>
+      <c r="G231" s="0">
+        <v>105</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
